--- a/public/assets/experiencia.xlsx
+++ b/public/assets/experiencia.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Página1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,9 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Title</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Position</t>
   </si>
   <si>
     <t>Description</t>
@@ -22,32 +28,58 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Trilogic - Uma plataforma de auxílio ao ensino e aprendizagem de lógica de programação (Projeto Acadêmico)</t>
+    <t>Target IT</t>
+  </si>
+  <si>
+    <t>Lavavel, ReactJS, Azure, API, Webservices, Postman</t>
+  </si>
+  <si>
+    <t>Desenvolvedora de Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atuo como Desenvolvedora de Software, contribuindo para a resolução de bugs e desenvolvimento de funcionalidades nas plataformas da empresa (ReactJS e Laravel). </t>
+  </si>
+  <si>
+    <t>Dezembro, 2025 - Presente</t>
+  </si>
+  <si>
+    <t>Diário Escola</t>
+  </si>
+  <si>
+    <t>HTML, CSS, JavaScript, PHP, Java, Objective C, SCRUM, Miro, API, Postman, Swagger, Confluence, Jira</t>
+  </si>
+  <si>
+    <t>Atuava como Desenvolvedora de Software Júnior, contribuindo para a resolução de bugs e desenvolvimento de funcionalidades nas plataformas Web (HTML, CSS, JavaScript, PHP), Android (Java) e iOS (Objective-C). Era responsável pela construção de interfaces de usuário responsivas e pela integração de APIs REST, além de participar de cerimônias SCRUM focadas na análise de requisitos e no planejamento de tarefas. Lidero o desenvolvimento de um projeto de integração, colaborando na arquitetura de uma nova solução com fluxos redesenhados, regras de negócio atualizadas, novas estruturas de banco de dados (campos e tabelas) e especificações de API, utilizando o Miro para mapeamento e documentação. Também dei suporte ao projeto durante sua implementação, resolução de bugs e assistência ao cliente.</t>
+  </si>
+  <si>
+    <t>Junho, 2023 - Novembro, 2025</t>
+  </si>
+  <si>
+    <t>Logimix (Projeto Acadêmico)</t>
+  </si>
+  <si>
+    <t>Canva, Google Planilhas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Manager Junior </t>
+  </si>
+  <si>
+    <t>Planejei e ministrei oficinas de robótica em escolas locais e comunidades vizinhas, criei conteúdo visual e escrito para as redes sociais e gerenciei a divulgação do projeto. Também documentei as etapas e atividades das oficinas para relatórios internos e externos e colaborei com a equipe para promover o desenvolvimento do pensamento computacional através da robótica educacional.</t>
+  </si>
+  <si>
+    <t>Janeiro, 2022 - Dezembro, 2022</t>
+  </si>
+  <si>
+    <t>Trilogic (Projeto Acadêmico)</t>
+  </si>
+  <si>
+    <t>Canva, WordPress, Google Planilhas</t>
   </si>
   <si>
     <t>Organizei e liderei tarefas e reuniões de equipe, testei e avaliei a plataforma educacional, e projetei uma nova identidade visual e experiência do usuário para a plataforma web. Também ministrei oficinas de lógica de programação para estudantes do ensino médio, realizei a manutenção e atualização do site do projeto utilizando WordPress, e gerenciei as redes sociais do projeto para compartilhar atualizações e engajar com o público.</t>
   </si>
   <si>
-    <t>Jan, 2021 - Dez, 2021</t>
-  </si>
-  <si>
-    <t>Logimix - Oficinas de Robótica Educativa na Educação Profissional (Projeto Acadêmico)</t>
-  </si>
-  <si>
-    <t>Planejei e ministrei oficinas de robótica em escolas locais e comunidades vizinhas, criei conteúdo visual e escrito para as redes sociais e gerenciei a divulgação do projeto. Também documentei as etapas e atividades das oficinas para relatórios internos e externos e colaborei com a equipe para promover o desenvolvimento do pensamento computacional através da robótica educacional.</t>
-  </si>
-  <si>
-    <t>Jan, 2022 - Dez, 2022</t>
-  </si>
-  <si>
-    <t>Desenvolvedora de Software Junior</t>
-  </si>
-  <si>
-    <t>Atuo como Desenvolvedora de Software Júnior, contribuindo para a resolução de bugs e desenvolvimento de funcionalidades nas plataformas Web (HTML, CSS, JavaScript, PHP), Android (Java) e iOS (Objective-C). Sou responsável pela construção de interfaces de usuário responsivas e pela integração de APIs REST, além de participar de cerimônias SCRUM focadas na análise de requisitos e no planejamento de tarefas.
-Atualmente, lidero o desenvolvimento de um projeto de integração, colaborando na arquitetura de uma nova solução com fluxos redesenhados, regras de negócio atualizadas, novas estruturas de banco de dados (campos e tabelas) e especificações de API, utilizando o Miro para mapeamento e documentação. Também dou suporte ao projeto durante sua implementação, resolução de bugs e assistência ao cliente.</t>
-  </si>
-  <si>
-    <t>Jun, 2023 - Presente</t>
+    <t>Janeiro, 2021 - Dezembro, 2021</t>
   </si>
 </sst>
 </file>
@@ -90,9 +122,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -113,6 +148,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -326,38 +365,79 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/experiencia.xlsx
+++ b/public/assets/experiencia.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Company</t>
   </si>
@@ -34,10 +34,10 @@
     <t>Lavavel, ReactJS, Azure, API, Webservices, Postman</t>
   </si>
   <si>
-    <t>Desenvolvedora de Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atuo como Desenvolvedora de Software, contribuindo para a resolução de bugs e desenvolvimento de funcionalidades nas plataformas da empresa (ReactJS e Laravel). </t>
+    <t>Desenvolvedora de Software IV</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de soluções fiscais e financeiras escaláveis com Laravel e ReactJS. Design e integração de APIs REST e Webservices com ERPs e plataformas externas. Implementação de regras de negócio complexas para portais de fornecedores e sistemas corporativos.</t>
   </si>
   <si>
     <t>Dezembro, 2025 - Presente</t>
@@ -49,37 +49,13 @@
     <t>HTML, CSS, JavaScript, PHP, Java, Objective C, SCRUM, Miro, API, Postman, Swagger, Confluence, Jira</t>
   </si>
   <si>
-    <t>Atuava como Desenvolvedora de Software Júnior, contribuindo para a resolução de bugs e desenvolvimento de funcionalidades nas plataformas Web (HTML, CSS, JavaScript, PHP), Android (Java) e iOS (Objective-C). Era responsável pela construção de interfaces de usuário responsivas e pela integração de APIs REST, além de participar de cerimônias SCRUM focadas na análise de requisitos e no planejamento de tarefas. Lidero o desenvolvimento de um projeto de integração, colaborando na arquitetura de uma nova solução com fluxos redesenhados, regras de negócio atualizadas, novas estruturas de banco de dados (campos e tabelas) e especificações de API, utilizando o Miro para mapeamento e documentação. Também dei suporte ao projeto durante sua implementação, resolução de bugs e assistência ao cliente.</t>
+    <t>Desenvolvedora de Software Júnior III.II</t>
+  </si>
+  <si>
+    <t>Desenvolvimento e manutenção de aplicações Web, Android (Java) e iOS (Objective-C). Criação de layouts responsivos e consumo de APIs REST. Definição de arquitetura, modelagem de banco de dados e regras de negócio para projetos de integração. Mapeamento de processos e documentação técnica via Miro. Análise de requisitos e planejamento em ambiente SCRUM. Suporte técnico à implementação e atendimento ao cliente.</t>
   </si>
   <si>
     <t>Junho, 2023 - Novembro, 2025</t>
-  </si>
-  <si>
-    <t>Logimix (Projeto Acadêmico)</t>
-  </si>
-  <si>
-    <t>Canva, Google Planilhas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Manager Junior </t>
-  </si>
-  <si>
-    <t>Planejei e ministrei oficinas de robótica em escolas locais e comunidades vizinhas, criei conteúdo visual e escrito para as redes sociais e gerenciei a divulgação do projeto. Também documentei as etapas e atividades das oficinas para relatórios internos e externos e colaborei com a equipe para promover o desenvolvimento do pensamento computacional através da robótica educacional.</t>
-  </si>
-  <si>
-    <t>Janeiro, 2022 - Dezembro, 2022</t>
-  </si>
-  <si>
-    <t>Trilogic (Projeto Acadêmico)</t>
-  </si>
-  <si>
-    <t>Canva, WordPress, Google Planilhas</t>
-  </si>
-  <si>
-    <t>Organizei e liderei tarefas e reuniões de equipe, testei e avaliei a plataforma educacional, e projetei uma nova identidade visual e experiência do usuário para a plataforma web. Também ministrei oficinas de lógica de programação para estudantes do ensino médio, realizei a manutenção e atualização do site do projeto utilizando WordPress, e gerenciei as redes sociais do projeto para compartilhar atualizações e engajar com o público.</t>
-  </si>
-  <si>
-    <t>Janeiro, 2021 - Dezembro, 2021</t>
   </si>
 </sst>
 </file>
@@ -397,47 +373,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
